--- a/test_data/norfolk_coastal_flooding/cpu_benchmarking_analysis_swmm.xlsx
+++ b/test_data/norfolk_coastal_flooding/cpu_benchmarking_analysis_swmm.xlsx
@@ -425,48 +425,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sa_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>run_mode</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_omp_threads</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>openmp</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>openmp</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>serial</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
     </row>
